--- a/Design/config/SkillConfig.xlsx
+++ b/Design/config/SkillConfig.xlsx
@@ -2385,134 +2385,134 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>给与我方前排士兵12%生命值护盾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>乱战</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击晕眩单位造成额外伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>晕眩流</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>luan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>乱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物标签</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SummonTag</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>武</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰流</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升本方火焰持续时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModifySummonTime</t>
+  </si>
+  <si>
+    <t>炽热</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>炽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>炽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckAttrs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>白</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陷阵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击几率使目标增伤40%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击几率使目标减速30%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击几率使目标陷阵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击几率使目标溃败</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>溃散</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>溃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>kui</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>xian</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>AttackPointReduce</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>给与我方前排士兵12%生命值护盾</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>乱战</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击晕眩单位造成额外伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>晕眩流</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>luan</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>乱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>召唤物标签</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SummonTag</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>武</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>火焰流</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升本方火焰持续时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ModifySummonTime</t>
-  </si>
-  <si>
-    <t>炽热</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>炽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>chi</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>炽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CheckAttrs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>纷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>白</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>陷阵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击几率使目标增伤40%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击几率使目标减速30%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击几率使目标陷阵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击几率使目标溃败</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>溃散</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>溃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>陷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>kui</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>xian</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6012,7 +6012,7 @@
         <v>535</v>
       </c>
       <c r="AE1" s="23" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AF1" s="23" t="s">
         <v>476</v>
@@ -6077,7 +6077,7 @@
         <v>26</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>424</v>
@@ -6086,7 +6086,7 @@
         <v>158</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>35</v>
@@ -6131,7 +6131,7 @@
         <v>456</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AC2" s="3" t="s">
         <v>467</v>
@@ -6140,7 +6140,7 @@
         <v>32</v>
       </c>
       <c r="AE2" s="24" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AF2" s="24" t="s">
         <v>131</v>
@@ -8357,7 +8357,7 @@
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="5">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="R29" s="36"/>
       <c r="S29" s="36"/>
@@ -8455,7 +8455,7 @@
       <c r="AC30" s="5"/>
       <c r="AD30" s="5"/>
       <c r="AE30" s="44" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AF30" s="44"/>
       <c r="AG30" s="44">
@@ -8607,7 +8607,7 @@
         <v>0.3</v>
       </c>
       <c r="I32" s="5">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
@@ -8715,7 +8715,7 @@
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="R33" s="36"/>
       <c r="S33" s="36"/>
@@ -8733,7 +8733,7 @@
       <c r="AC33" s="5"/>
       <c r="AD33" s="5"/>
       <c r="AE33" s="44" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AF33" s="44"/>
       <c r="AG33" s="44">
@@ -8879,7 +8879,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="5">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="J35" s="5">
         <v>2</v>
@@ -8890,19 +8890,19 @@
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="5">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="R35" s="36"/>
       <c r="S35" s="36"/>
       <c r="T35" s="40"/>
       <c r="U35" s="40"/>
       <c r="V35" s="40">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="W35" s="5"/>
       <c r="X35" s="5"/>
@@ -8913,14 +8913,14 @@
       <c r="AC35" s="5"/>
       <c r="AD35" s="5"/>
       <c r="AE35" s="44" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AF35" s="44"/>
       <c r="AG35" s="44">
         <v>11</v>
       </c>
       <c r="AH35" s="44">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" s="44"/>
       <c r="AJ35" s="44">
@@ -9520,16 +9520,16 @@
         <v>201024</v>
       </c>
       <c r="B43" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>605</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>609</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>606</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5">
@@ -9586,7 +9586,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AQ43">
         <f>COUNTIF([1]Sheet1!$R:$U,C43)</f>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F62" s="9"/>
       <c r="G62" s="5">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F63" s="9"/>
       <c r="G63" s="5">
@@ -11154,14 +11154,14 @@
         <v>203007</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F64" s="9"/>
       <c r="G64" s="5">
@@ -11220,7 +11220,7 @@
         <v>2</v>
       </c>
       <c r="AP64" s="57" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AQ64">
         <f>COUNTIF([1]Sheet1!$R:$U,C64)</f>
@@ -11232,14 +11232,14 @@
         <v>203008</v>
       </c>
       <c r="B65" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="C65" s="9" t="s">
         <v>630</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>631</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F65" s="9"/>
       <c r="G65" s="5">
@@ -11300,7 +11300,7 @@
         <v>2</v>
       </c>
       <c r="AP65" s="57" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AQ65">
         <f>COUNTIF([1]Sheet1!$R:$U,C65)</f>
@@ -11399,7 +11399,7 @@
         <v>444</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D67" s="48"/>
       <c r="E67" s="48" t="s">
@@ -11561,7 +11561,7 @@
         <v>378</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
@@ -12034,16 +12034,16 @@
         <v>208008</v>
       </c>
       <c r="B75" s="17" t="s">
+        <v>617</v>
+      </c>
+      <c r="C75" s="12" t="s">
         <v>618</v>
       </c>
-      <c r="C75" s="12" t="s">
-        <v>619</v>
-      </c>
       <c r="D75" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="E75" s="5" t="s">
         <v>615</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>616</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>255</v>
@@ -12074,7 +12074,7 @@
         <v>3</v>
       </c>
       <c r="Z75" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AA75" s="8"/>
       <c r="AB75" s="5"/>
@@ -12091,7 +12091,7 @@
       <c r="AI75" s="44"/>
       <c r="AJ75" s="44"/>
       <c r="AK75" s="59" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AL75" s="52"/>
       <c r="AM75" s="52"/>
@@ -12100,7 +12100,7 @@
         <v>2</v>
       </c>
       <c r="AP75" s="55" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AQ75">
         <f>COUNTIF([1]Sheet1!$R:$U,C75)</f>
@@ -12339,7 +12339,7 @@
         <v>572</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F79" s="11"/>
       <c r="G79" s="5">
